--- a/Documentation/Best For Weighting Tables/Best Premium Robotic Pets.xlsx
+++ b/Documentation/Best For Weighting Tables/Best Premium Robotic Pets.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\Best For Weighting Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C551DFA4-AB11-4463-A613-E566FD46CEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED60714-D68F-4EF1-899E-F1AA41479166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="2430" windowWidth="21600" windowHeight="11295" xr2:uid="{836AF667-51B2-4114-83FE-09F3245F9CFE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{836AF667-51B2-4114-83FE-09F3245F9CFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Best Premium Robotic Pets_x0009_" sheetId="1" r:id="rId1"/>
+    <sheet name="Filters" sheetId="3" r:id="rId2"/>
+    <sheet name="Lists" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>Feature</t>
   </si>
@@ -81,6 +83,33 @@
   </si>
   <si>
     <t>Value for money</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>equal</t>
+  </si>
+  <si>
+    <t>not equal</t>
+  </si>
+  <si>
+    <t>less thatn</t>
+  </si>
+  <si>
+    <t>greater than</t>
+  </si>
+  <si>
+    <t>Price Category</t>
+  </si>
+  <si>
+    <t>Premium</t>
   </si>
 </sst>
 </file>
@@ -124,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -141,6 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -582,4 +612,84 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F12D44D-865A-48D0-87A5-3AF5AAB9F5FA}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A4E8B464-B7C6-4462-B7BF-4455905248D7}">
+          <x14:formula1>
+            <xm:f>Lists!$A$1:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1:B1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D485AB-7D97-4A82-947E-240EB0C69CEB}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>